--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/WEST_VIRGINIA_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/WEST_VIRGINIA_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BEJUCAL DE OCAMPO</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHAMULA</t>
+          <t>Chamula</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESCUINTLA</t>
+          <t>Escuintla</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FRONTERA COMALAPA</t>
+          <t>Frontera Comalapa</t>
         </is>
       </c>
       <c r="C5">
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HUIXTÁN</t>
+          <t>Huixtán</t>
         </is>
       </c>
       <c r="C6">
@@ -447,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA CONCORDIA</t>
+          <t>La Concordia</t>
         </is>
       </c>
       <c r="C7">
@@ -460,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAZAPA DE MADERO</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C8">
@@ -473,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOTOZINTLA</t>
+          <t>Motozintla</t>
         </is>
       </c>
       <c r="C9">
@@ -486,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OCOSINGO</t>
+          <t>Ocosingo</t>
         </is>
       </c>
       <c r="C10">
@@ -499,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANTELHÓ</t>
+          <t>Pantelhó</t>
         </is>
       </c>
       <c r="C11">
@@ -512,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAN CRISTÓBAL DE LAS CASAS</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C12">
@@ -525,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TAPALAPA</t>
+          <t>Tapalapa</t>
         </is>
       </c>
       <c r="C13">
@@ -538,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TECPATÁN</t>
+          <t>Tecpatán</t>
         </is>
       </c>
       <c r="C14">
@@ -551,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VILLA CORZO</t>
+          <t>Villa Corzo</t>
         </is>
       </c>
       <c r="C15">
@@ -564,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C16">
@@ -579,12 +649,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C17">
@@ -595,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IZTACALCO</t>
+          <t>Iztacalco</t>
         </is>
       </c>
       <c r="C18">
@@ -608,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NEZAHUALCÓYOTL</t>
+          <t>Nezahualcóyotl</t>
         </is>
       </c>
       <c r="C19">
@@ -621,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XOCHIMILCO</t>
+          <t>Xochimilco</t>
         </is>
       </c>
       <c r="C20">
@@ -634,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C21">
@@ -649,12 +739,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLIMA</t>
+          <t>Colima</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IXTLAHUACÁN</t>
+          <t>Ixtlahuacán</t>
         </is>
       </c>
       <c r="C22">
@@ -665,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C23">
@@ -680,12 +775,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="C24">
@@ -696,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C25">
@@ -711,12 +811,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NEZAHUALCÓYOTL</t>
+          <t>Nezahualcóyotl</t>
         </is>
       </c>
       <c r="C26">
@@ -727,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SULTEPEC</t>
+          <t>Sultepec</t>
         </is>
       </c>
       <c r="C27">
@@ -740,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>Tenancingo</t>
         </is>
       </c>
       <c r="C28">
@@ -753,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TLATLAYA</t>
+          <t>Tlatlaya</t>
         </is>
       </c>
       <c r="C29">
@@ -766,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TOLUCA</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="C30">
@@ -779,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZACUALPAN</t>
+          <t>Zacualpan</t>
         </is>
       </c>
       <c r="C31">
@@ -792,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C32">
@@ -807,12 +937,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CUERÁMARO</t>
+          <t>Cuerámaro</t>
         </is>
       </c>
       <c r="C33">
@@ -823,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MANUEL DOBLADO</t>
+          <t>Manuel Doblado</t>
         </is>
       </c>
       <c r="C34">
@@ -836,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C35">
@@ -851,12 +991,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AJUCHITLÁN DEL PROGRESO</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C36">
@@ -867,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ATOYAC DE ÁLVAREZ</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C37">
@@ -880,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C38">
@@ -893,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CHILAPA DE ÁLVAREZ</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C39">
@@ -906,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHILPANCINGO DE LOS BRAVO</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C40">
@@ -919,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COYUCA DE CATALÁN</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C41">
@@ -932,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GENERAL CANUTO A. NERI</t>
+          <t>General Canuto A. Neri</t>
         </is>
       </c>
       <c r="C42">
@@ -945,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MALINALTEPEC</t>
+          <t>Malinaltepec</t>
         </is>
       </c>
       <c r="C43">
@@ -958,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OMETEPEC</t>
+          <t>Ometepec</t>
         </is>
       </c>
       <c r="C44">
@@ -971,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PEDRO ASCENCIO ALQUISIRAS</t>
+          <t>Pedro Ascencio Alquisiras</t>
         </is>
       </c>
       <c r="C45">
@@ -984,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PETATLÁN</t>
+          <t>Petatlán</t>
         </is>
       </c>
       <c r="C46">
@@ -997,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZIHUATANEJO DE AZUETA</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C47">
@@ -1010,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C48">
@@ -1025,12 +1225,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ATOTONILCO EL GRANDE</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C49">
@@ -1041,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HUASCA DE OCAMPO</t>
+          <t>Huasca De Ocampo</t>
         </is>
       </c>
       <c r="C50">
@@ -1054,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MINERAL DEL CHICO</t>
+          <t>Mineral Del Chico</t>
         </is>
       </c>
       <c r="C51">
@@ -1067,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MIXQUIAHUALA DE JUÁREZ</t>
+          <t>Mixquiahuala De Juárez</t>
         </is>
       </c>
       <c r="C52">
@@ -1080,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SANTIAGO DE ANAYA</t>
+          <t>Santiago De Anaya</t>
         </is>
       </c>
       <c r="C53">
@@ -1093,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TECOZAUTLA</t>
+          <t>Tecozautla</t>
         </is>
       </c>
       <c r="C54">
@@ -1106,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZACUALTIPÁN DE ÁNGELES</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C55">
@@ -1119,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C56">
@@ -1134,12 +1369,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ACATIC</t>
+          <t>Acatic</t>
         </is>
       </c>
       <c r="C57">
@@ -1150,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENCARNACIÓN DE DÍAZ</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C58">
@@ -1163,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C59">
@@ -1176,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JESÚS MARÍA</t>
+          <t>Jesús María</t>
         </is>
       </c>
       <c r="C60">
@@ -1189,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OJUELOS DE JALISCO</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C61">
@@ -1202,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZAPOPAN</t>
+          <t>Zapopan</t>
         </is>
       </c>
       <c r="C62">
@@ -1215,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C63">
@@ -1230,12 +1495,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>APATZINGÁN</t>
+          <t>Apatzingán</t>
         </is>
       </c>
       <c r="C64">
@@ -1246,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AQUILA</t>
+          <t>Aquila</t>
         </is>
       </c>
       <c r="C65">
@@ -1259,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>INDAPARAPEO</t>
+          <t>Indaparapeo</t>
         </is>
       </c>
       <c r="C66">
@@ -1272,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LA PIEDAD</t>
+          <t>La Piedad</t>
         </is>
       </c>
       <c r="C67">
@@ -1285,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t>Morelia</t>
         </is>
       </c>
       <c r="C68">
@@ -1298,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PARACHO</t>
+          <t>Paracho</t>
         </is>
       </c>
       <c r="C69">
@@ -1311,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PURÉPERO</t>
+          <t>Purépero</t>
         </is>
       </c>
       <c r="C70">
@@ -1324,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAN LUCAS</t>
+          <t>San Lucas</t>
         </is>
       </c>
       <c r="C71">
@@ -1337,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TIQUICHEO DE NICOLÁS ROMERO</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C72">
@@ -1350,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>URUAPAN</t>
+          <t>Uruapan</t>
         </is>
       </c>
       <c r="C73">
@@ -1363,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C74">
@@ -1378,12 +1693,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AYOTZINTEPEC</t>
+          <t>Ayotzintepec</t>
         </is>
       </c>
       <c r="C75">
@@ -1394,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE TLAXIACO</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C76">
@@ -1407,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAN CARLOS YAUTEPEC</t>
+          <t>San Carlos Yautepec</t>
         </is>
       </c>
       <c r="C77">
@@ -1420,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAN MIGUEL PANIXTLAHUACA</t>
+          <t>San Miguel Panixtlahuaca</t>
         </is>
       </c>
       <c r="C78">
@@ -1433,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAN PEDRO MIXTEPEC -DTO. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C79">
@@ -1446,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SAN PEDRO MÁRTIR</t>
+          <t>San Pedro Mártir</t>
         </is>
       </c>
       <c r="C80">
@@ -1459,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SAN PEDRO POCHUTLA</t>
+          <t>San Pedro Pochutla</t>
         </is>
       </c>
       <c r="C81">
@@ -1472,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SAN PEDRO TEUTILA</t>
+          <t>San Pedro Teutila</t>
         </is>
       </c>
       <c r="C82">
@@ -1485,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SANTA CATARINA JUQUILA</t>
+          <t>Santa Catarina Juquila</t>
         </is>
       </c>
       <c r="C83">
@@ -1498,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SANTA MARÍA COLOTEPEC</t>
+          <t>Santa María Colotepec</t>
         </is>
       </c>
       <c r="C84">
@@ -1511,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SANTA MARÍA ZACATEPEC</t>
+          <t>Santa María Zacatepec</t>
         </is>
       </c>
       <c r="C85">
@@ -1524,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SANTIAGO CAMOTLÁN</t>
+          <t>Santiago Camotlán</t>
         </is>
       </c>
       <c r="C86">
@@ -1537,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SANTIAGO JAMILTEPEC</t>
+          <t>Santiago Jamiltepec</t>
         </is>
       </c>
       <c r="C87">
@@ -1550,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE MORELOS</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C88">
@@ -1563,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SANTOS REYES NOPALA</t>
+          <t>Santos Reyes Nopala</t>
         </is>
       </c>
       <c r="C89">
@@ -1576,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C90">
@@ -1591,12 +1981,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HUAQUECHULA</t>
+          <t>Huaquechula</t>
         </is>
       </c>
       <c r="C91">
@@ -1607,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HUEJOTZINGO</t>
+          <t>Huejotzingo</t>
         </is>
       </c>
       <c r="C92">
@@ -1620,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C93">
@@ -1633,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C94">
@@ -1646,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C95">
@@ -1661,12 +2071,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PEÑAMILLER</t>
+          <t>Peñamiller</t>
         </is>
       </c>
       <c r="C96">
@@ -1677,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAN JUAN DEL RÍO</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C97">
@@ -1690,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C98">
@@ -1705,12 +2125,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>QUINTANA ROO</t>
+          <t>Quintana Roo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OTHÓN P. BLANCO</t>
+          <t>Othón P. Blanco</t>
         </is>
       </c>
       <c r="C99">
@@ -1721,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C100">
@@ -1736,12 +2161,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HUEHUETLÁN</t>
+          <t>Huehuetlán</t>
         </is>
       </c>
       <c r="C101">
@@ -1752,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RIOVERDE</t>
+          <t>Rioverde</t>
         </is>
       </c>
       <c r="C102">
@@ -1765,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VILLA HIDALGO</t>
+          <t>Villa Hidalgo</t>
         </is>
       </c>
       <c r="C103">
@@ -1778,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C104">
@@ -1793,12 +2233,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AHOME</t>
+          <t>Ahome</t>
         </is>
       </c>
       <c r="C105">
@@ -1809,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C106">
@@ -1824,12 +2269,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TABASCO</t>
+          <t>Tabasco</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="C107">
@@ -1840,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CÁRDENAS</t>
+          <t>Cárdenas</t>
         </is>
       </c>
       <c r="C108">
@@ -1853,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C109">
@@ -1868,12 +2323,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TAMPICO</t>
+          <t>Tampico</t>
         </is>
       </c>
       <c r="C110">
@@ -1884,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C111">
@@ -1899,12 +2359,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ALTOTONGA</t>
+          <t>Altotonga</t>
         </is>
       </c>
       <c r="C112">
@@ -1915,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ATZACAN</t>
+          <t>Atzacan</t>
         </is>
       </c>
       <c r="C113">
@@ -1928,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CALCAHUALCO</t>
+          <t>Calcahualco</t>
         </is>
       </c>
       <c r="C114">
@@ -1941,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CÓRDOBA</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="C115">
@@ -1954,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HUATUSCO</t>
+          <t>Huatusco</t>
         </is>
       </c>
       <c r="C116">
@@ -1967,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IGNACIO DE LA LLAVE</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C117">
@@ -1980,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LAS CHOAPAS</t>
+          <t>Las Choapas</t>
         </is>
       </c>
       <c r="C118">
@@ -1993,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MARIANO ESCOBEDO</t>
+          <t>Mariano Escobedo</t>
         </is>
       </c>
       <c r="C119">
@@ -2006,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MARTÍNEZ DE LA TORRE</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C120">
@@ -2019,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MINATITLÁN</t>
+          <t>Minatitlán</t>
         </is>
       </c>
       <c r="C121">
@@ -2032,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>OMEALCA</t>
+          <t>Omealca</t>
         </is>
       </c>
       <c r="C122">
@@ -2045,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PLAYA VICENTE</t>
+          <t>Playa Vicente</t>
         </is>
       </c>
       <c r="C123">
@@ -2058,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>POZA RICA DE HIDALGO</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C124">
@@ -2071,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS TUXTLA</t>
+          <t>San Andrés Tuxtla</t>
         </is>
       </c>
       <c r="C125">
@@ -2084,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TEZONAPA</t>
+          <t>Tezonapa</t>
         </is>
       </c>
       <c r="C126">
@@ -2097,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TLAQUILPA</t>
+          <t>Tlaquilpa</t>
         </is>
       </c>
       <c r="C127">
@@ -2110,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TOMATLÁN</t>
+          <t>Tomatlán</t>
         </is>
       </c>
       <c r="C128">
@@ -2123,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C129">
@@ -2138,12 +2683,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JEREZ</t>
+          <t>Jerez</t>
         </is>
       </c>
       <c r="C130">
@@ -2154,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PINOS</t>
+          <t>Pinos</t>
         </is>
       </c>
       <c r="C131">
@@ -2167,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SOMBRERETE</t>
+          <t>Sombrerete</t>
         </is>
       </c>
       <c r="C132">
@@ -2180,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VALPARAÍSO</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C133">
@@ -2193,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C134">
@@ -2208,7 +2773,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C135">
@@ -2216,41 +2781,6 @@
       </c>
       <c r="D135">
         <v>1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
